--- a/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:02</t>
+          <t>2026-10-06 01:23:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:04</t>
+          <t>2026-10-06 01:23:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:05</t>
+          <t>2026-10-06 01:23:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 01:15:06</t>
+          <t>2026-10-06 01:24:01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:57</t>
+          <t>2026-10-06 02:27:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:58</t>
+          <t>2026-10-06 02:27:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:59</t>
+          <t>2026-10-06 02:27:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:01</t>
+          <t>2026-10-06 02:27:36</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.66%1,794,000</t>
+          <t>8.61%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.66%</t>
+          <t>8.61%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.03%736,000</t>
+          <t>7.09%736,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.03%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+4.06%615</t>
+          <t>-3.74%592</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>615</v>
+        <v>592</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.51%5,709,000</t>
+          <t>6.55%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.55%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.94%790</t>
+          <t>+0.63%795</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.56%3,715,000</t>
+          <t>5.52%3,745,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3715000</v>
+        <v>3745000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.20%179,000</t>
+          <t>4.46%179,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.09%1,016,225</t>
+          <t>4.07%1,016,225</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.5%1055</t>
+          <t>-0.95%1045</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.94%2,041,000</t>
+          <t>4.01%2,041,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.57%845,000</t>
+          <t>3.66%845,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.67%576</t>
+          <t>+5.21%1715</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>576</v>
+        <v>1715</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.42%3,158,000</t>
+          <t>3.59%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3158000</v>
+        <v>1180000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.76%1630</t>
+          <t>-0.35%574</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.76%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1630</v>
+        <v>574</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.38%1,180,000</t>
+          <t>3.39%3,158,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1180000</v>
+        <v>3158000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.09%309,000</t>
+          <t>3.28%309,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5520</v>
+        <v>6855</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.08%301,000</t>
+          <t>3.15%251,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>301000</v>
+        <v>251000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6730</v>
+        <v>5670</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.05%251,000</t>
+          <t>3.10%301,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>251000</v>
+        <v>301000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,25 +1297,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.84%1180</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1180</v>
+        <v>3685</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.49%1,082,000</t>
+          <t>2.49%372,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1324,11 +1324,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1082000</v>
+        <v>372000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:32</t>
+          <t>2026-10-06 19:16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.12%1205</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3585</v>
+        <v>1205</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.47%372,000</t>
+          <t>2.38%1,082,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>372000</v>
+        <v>1082000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.86%298</t>
+          <t>+0.34%299</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.75%3,216,000</t>
+          <t>1.79%3,216,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+4.48%606</t>
+          <t>-6.44%567</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.71%1,529,000</t>
+          <t>1.73%1,529,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.59%5,116,000</t>
+          <t>1.45%5,116,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.16%214.5</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>214.5</v>
+        <v>1755</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.46%3,415,000</t>
+          <t>1.39%418,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3415000</v>
+        <v>418000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.35%740</t>
+          <t>+0.23%215</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>740</v>
+        <v>215</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.33%964,000</t>
+          <t>1.37%3,415,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>964000</v>
+        <v>3415000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.61%189.5</t>
+          <t>-0.27%738</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>189.5</v>
+        <v>738</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.31%3,638,000</t>
+          <t>1.33%964,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3638000</v>
+        <v>964000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>+4.79%787</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1780</v>
+        <v>787</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.31%418,000</t>
+          <t>1.32%940,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>418000</v>
+        <v>940000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>19520</v>
+        <v>18985</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.43%105.5</t>
+          <t>0%189.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>105.5</v>
+        <v>189.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.26%6,382,000</t>
+          <t>1.29%3,638,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>6382000</v>
+        <v>3638000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+4.02%388.5</t>
+          <t>-2.19%380</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>388.5</v>
+        <v>380</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25%1,737,000</t>
+          <t>1.26%1,737,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%188.5</t>
+          <t>-4.74%100.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>188.5</v>
+        <v>100.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.25%3,438,000</t>
+          <t>1.26%6,382,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3438000</v>
+        <v>6382000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.96%751</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.24%940,000</t>
+          <t>1.21%876,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>940000</v>
+        <v>876000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%188</t>
+          <t>0%188.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2165,11 +2165,11 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>188</v>
+        <v>188.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.21%3,345,000</t>
+          <t>1.21%3,438,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3345000</v>
+        <v>3438000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+5.05%197.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>742</v>
+        <v>197.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.21%876,000</t>
+          <t>1.17%3,345,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>876000</v>
+        <v>3345000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:33</t>
+          <t>2026-10-06 19:16:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.38%262</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>262</v>
+        <v>1600</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.15%2,268,000</t>
+          <t>1.14%382,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2268000</v>
+        <v>382000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.41%297.5</t>
+          <t>+0.19%262.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.41%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>297.5</v>
+        <v>262.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%1,910,000</t>
+          <t>1.11%2,268,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1910000</v>
+        <v>2268000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>+2.42%762</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1595</v>
+        <v>762</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.11%382,000</t>
+          <t>1.10%790,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>382000</v>
+        <v>790000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+3.19%744</t>
+          <t>-0.17%576</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>744</v>
+        <v>576</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.10%790,000</t>
+          <t>1.08%1,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>790000</v>
+        <v>1000000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.29%173</t>
+          <t>+4.37%310.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+4.37%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>173</v>
+        <v>310.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.10%3,280,000</t>
+          <t>1.06%1,910,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>3280000</v>
+        <v>1910000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.53%577</t>
+          <t>0%173</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>577</v>
+        <v>173</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.07%1,000,000</t>
+          <t>1.06%3,280,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000000</v>
+        <v>3280000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.39%126.5</t>
+          <t>+1.58%128.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+1.58%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>126.5</v>
+        <v>128.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.06%4,331,000</t>
+          <t>1.02%4,331,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.00%3,344,000</t>
+          <t>0.97%3,344,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>+4.19%994</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+4.19%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2075</v>
+        <v>994</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.84%222,000</t>
+          <t>0.81%455,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>222000</v>
+        <v>455000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.21%954</t>
+          <t>-0.95%416.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>954</v>
+        <v>416.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.84%455,000</t>
+          <t>0.81%1,032,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>455000</v>
+        <v>1032000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%420.5</t>
+          <t>-2.43%241</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>420.5</v>
+        <v>241</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.84%1,032,000</t>
+          <t>0.74%1,607,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1032000</v>
+        <v>1607000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.82%247</t>
+          <t>-1.27%3115</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>247</v>
+        <v>3115</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.76%1,607,000</t>
+          <t>0.55%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1607000</v>
+        <v>93000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.47%3155</t>
+          <t>+1.88%459.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3155</v>
+        <v>459.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.57%93,000</t>
+          <t>0.44%527,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>93000</v>
+        <v>527000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.73%451</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>451</v>
+        <v>2050</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.45%527,000</t>
+          <t>0.43%111,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>527000</v>
+        <v>111000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+9.87%679</t>
+          <t>-2.36%663</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+9.87%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.36%304,000</t>
+          <t>0.38%304,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:35</t>
+          <t>2026-10-06 19:16:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,33 +3193,33 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.97%51.7</t>
+          <t>-1.35%51</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.97%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>51.7</v>
+        <v>51</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%3,212,000</t>
+          <t>0.36%3,712,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>3212000</v>
+        <v>3712000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>6640均華</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.98%128.5</t>
+          <t>-2.58%1135</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>128.5</v>
+        <v>1135</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.31%1,281,000</t>
+          <t>0.31%143,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1281000</v>
+        <v>143000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,25 +3310,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6640均華</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+3.56%1165</t>
+          <t>+2.33%131.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1165</v>
+        <v>131.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.31%143,000</t>
+          <t>0.31%1,281,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>143000</v>
+        <v>1281000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.82%241.5</t>
+          <t>+1.45%245</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>241.5</v>
+        <v>245</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.29%627,000</t>
+          <t>0.28%627,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+2.1%68.2</t>
+          <t>+1.61%69.3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>68.2</v>
+        <v>69.3</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.29%2,213,556</t>
+          <t>0.28%2,213,556</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+2.15%1190</t>
+          <t>-1.26%1175</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1190</v>
+        <v>1175</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-1.52%45.3</t>
+          <t>-0.33%45.15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>45.3</v>
+        <v>45.15</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.29%169.5</t>
+          <t>0%169.5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+9.83%570</t>
+          <t>-3.33%551</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+9.83%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-0.14%691</t>
+          <t>+0.72%696</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.61%48.55</t>
+          <t>+1.54%49.3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>48.55</v>
+        <v>49.3</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:36</t>
+          <t>2026-10-06 19:16:34</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+1%152</t>
+          <t>+1.64%154.5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>152</v>
+        <v>154.5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:30</t>
+          <t>2026-10-06 23:19:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:31</t>
+          <t>2026-10-06 23:19:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:33</t>
+          <t>2026-10-06 23:19:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 19:16:34</t>
+          <t>2026-10-06 23:19:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:12</t>
+          <t>2026-10-06 23:27:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:13</t>
+          <t>2026-10-06 23:27:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:14</t>
+          <t>2026-10-06 23:27:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:15</t>
+          <t>2026-10-06 23:27:46</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:42</t>
+          <t>2026-10-06 23:58:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:43</t>
+          <t>2026-10-06 23:58:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:44</t>
+          <t>2026-10-06 23:58:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:46</t>
+          <t>2026-10-06 23:58:18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
